--- a/Tests/Validation/Canola/Greenethorpe2013.xlsx
+++ b/Tests/Validation/Canola/Greenethorpe2013.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lil026\ApsimX\Prototypes\Canola\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\ApsimX\Tests\Validation\Canola\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFAD32E0-6BAB-41C8-80BF-3A83274E5090}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD844B5-8002-4CBB-A03B-950EFCD174C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{82FDB4BE-E74B-4488-8680-42A462D2A87F}"/>
+    <workbookView xWindow="-27675" yWindow="1125" windowWidth="21600" windowHeight="11280" xr2:uid="{82FDB4BE-E74B-4488-8680-42A462D2A87F}"/>
   </bookViews>
   <sheets>
     <sheet name="Observed" sheetId="1" r:id="rId1"/>
@@ -84,9 +84,6 @@
     <t>Canola.Stem.NConc</t>
   </si>
   <si>
-    <t>Canola.Leaf.Live.Nconc</t>
-  </si>
-  <si>
     <t>Canola.Leaf.LAI</t>
   </si>
   <si>
@@ -108,9 +105,6 @@
     <t>Clock.Today</t>
   </si>
   <si>
-    <t>treat</t>
-  </si>
-  <si>
     <t>site</t>
   </si>
   <si>
@@ -138,9 +132,6 @@
     <t>Canola.Leaf.SpecificArea</t>
   </si>
   <si>
-    <t>Canola.Shell.Nconc</t>
-  </si>
-  <si>
     <t>Canola.DaysAfterSowing</t>
   </si>
   <si>
@@ -163,6 +154,15 @@
   </si>
   <si>
     <t>nil</t>
+  </si>
+  <si>
+    <t>Canola.Leaf.Live.NConc</t>
+  </si>
+  <si>
+    <t>Canola.Shell.NConc</t>
+  </si>
+  <si>
+    <t>Treat</t>
   </si>
 </sst>
 </file>
@@ -198,11 +198,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -221,9 +220,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -261,7 +260,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -367,7 +366,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -509,7 +508,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -551,82 +550,82 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="P1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U1" t="s">
+        <v>10</v>
+      </c>
+      <c r="V1" t="s">
+        <v>24</v>
+      </c>
+      <c r="W1" t="s">
+        <v>25</v>
+      </c>
+      <c r="X1" t="s">
         <v>34</v>
-      </c>
-      <c r="G1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M1" t="s">
-        <v>15</v>
-      </c>
-      <c r="N1" t="s">
-        <v>14</v>
-      </c>
-      <c r="O1" t="s">
-        <v>22</v>
-      </c>
-      <c r="P1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R1" t="s">
-        <v>24</v>
-      </c>
-      <c r="S1" t="s">
-        <v>25</v>
-      </c>
-      <c r="T1" t="s">
-        <v>12</v>
-      </c>
-      <c r="U1" t="s">
-        <v>11</v>
-      </c>
-      <c r="V1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W1" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" t="s">
-        <v>10</v>
       </c>
       <c r="Y1" t="s">
         <v>9</v>
       </c>
       <c r="Z1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="AA1" t="s">
         <v>8</v>
@@ -655,7 +654,7 @@
       <c r="G2" s="1">
         <v>41401</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2">
         <f>G2-F2</f>
         <v>43</v>
       </c>
@@ -704,7 +703,7 @@
       <c r="G3" s="1">
         <v>41444</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3">
         <f t="shared" ref="H3:H29" si="1">G3-F3</f>
         <v>86</v>
       </c>
@@ -753,7 +752,7 @@
       <c r="G4" s="1">
         <v>41479</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4">
         <f t="shared" si="1"/>
         <v>121</v>
       </c>
@@ -805,7 +804,7 @@
       <c r="G5" s="1">
         <v>41492</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5">
         <f t="shared" si="1"/>
         <v>134</v>
       </c>
@@ -857,7 +856,7 @@
       <c r="G6" s="1">
         <v>41528</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6">
         <f t="shared" si="1"/>
         <v>170</v>
       </c>
@@ -909,7 +908,7 @@
       <c r="G7" s="1">
         <v>41563</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7">
         <f t="shared" si="1"/>
         <v>205</v>
       </c>
@@ -955,7 +954,7 @@
       <c r="G8" s="1">
         <v>41582</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8">
         <f t="shared" si="1"/>
         <v>224</v>
       </c>
@@ -1014,7 +1013,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E9" t="s">
         <v>0</v>
@@ -1025,7 +1024,7 @@
       <c r="G9" s="1">
         <v>41470</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9">
         <f t="shared" si="1"/>
         <v>83</v>
       </c>
@@ -1048,7 +1047,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E10" t="s">
         <v>0</v>
@@ -1059,7 +1058,7 @@
       <c r="G10" s="1">
         <v>41479</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10">
         <f t="shared" si="1"/>
         <v>92</v>
       </c>
@@ -1100,7 +1099,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E11" t="s">
         <v>0</v>
@@ -1111,7 +1110,7 @@
       <c r="G11" s="1">
         <v>41485</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11">
         <f t="shared" si="1"/>
         <v>98</v>
       </c>
@@ -1152,7 +1151,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E12" t="s">
         <v>0</v>
@@ -1163,7 +1162,7 @@
       <c r="G12" s="1">
         <v>41492</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12">
         <f t="shared" si="1"/>
         <v>105</v>
       </c>
@@ -1204,7 +1203,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E13" t="s">
         <v>0</v>
@@ -1215,7 +1214,7 @@
       <c r="G13" s="1">
         <v>41515</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13">
         <f t="shared" si="1"/>
         <v>128</v>
       </c>
@@ -1256,7 +1255,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E14" t="s">
         <v>0</v>
@@ -1267,7 +1266,7 @@
       <c r="G14" s="1">
         <v>41570</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14">
         <f t="shared" si="1"/>
         <v>183</v>
       </c>
@@ -1337,7 +1336,7 @@
       <c r="G15" s="1">
         <v>41479</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15">
         <f t="shared" si="1"/>
         <v>92</v>
       </c>
@@ -1389,7 +1388,7 @@
       <c r="G16" s="1">
         <v>41479</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16">
         <f t="shared" si="1"/>
         <v>92</v>
       </c>
@@ -1430,7 +1429,7 @@
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E17" t="s">
         <v>0</v>
@@ -1441,7 +1440,7 @@
       <c r="G17" s="1">
         <v>41479</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17">
         <f t="shared" si="1"/>
         <v>92</v>
       </c>
@@ -1493,7 +1492,7 @@
       <c r="G18" s="1">
         <v>41485</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18">
         <f t="shared" si="1"/>
         <v>98</v>
       </c>
@@ -1551,7 +1550,7 @@
       <c r="G19" s="1">
         <v>41485</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19">
         <f t="shared" si="1"/>
         <v>98</v>
       </c>
@@ -1598,7 +1597,7 @@
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E20" t="s">
         <v>0</v>
@@ -1609,7 +1608,7 @@
       <c r="G20" s="1">
         <v>41485</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20">
         <f t="shared" si="1"/>
         <v>98</v>
       </c>
@@ -1667,7 +1666,7 @@
       <c r="G21" s="1">
         <v>41515</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21">
         <f t="shared" si="1"/>
         <v>128</v>
       </c>
@@ -1728,7 +1727,7 @@
       <c r="G22" s="1">
         <v>41515</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H22">
         <f t="shared" si="1"/>
         <v>128</v>
       </c>
@@ -1778,7 +1777,7 @@
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E23" t="s">
         <v>0</v>
@@ -1789,7 +1788,7 @@
       <c r="G23" s="1">
         <v>41515</v>
       </c>
-      <c r="H23" s="3">
+      <c r="H23">
         <f t="shared" si="1"/>
         <v>128</v>
       </c>
@@ -1850,7 +1849,7 @@
       <c r="G24" s="1">
         <v>41543</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24">
         <f t="shared" si="1"/>
         <v>156</v>
       </c>
@@ -1899,7 +1898,7 @@
       <c r="G25" s="1">
         <v>41543</v>
       </c>
-      <c r="H25" s="3">
+      <c r="H25">
         <f t="shared" si="1"/>
         <v>156</v>
       </c>
@@ -1937,7 +1936,7 @@
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E26" t="s">
         <v>0</v>
@@ -1948,7 +1947,7 @@
       <c r="G26" s="1">
         <v>41543</v>
       </c>
-      <c r="H26" s="3">
+      <c r="H26">
         <f t="shared" si="1"/>
         <v>156</v>
       </c>
@@ -1997,7 +1996,7 @@
       <c r="G27" s="1">
         <v>41570</v>
       </c>
-      <c r="H27" s="3">
+      <c r="H27">
         <f t="shared" si="1"/>
         <v>183</v>
       </c>
@@ -2070,7 +2069,7 @@
       <c r="G28" s="1">
         <v>41570</v>
       </c>
-      <c r="H28" s="3">
+      <c r="H28">
         <f t="shared" si="1"/>
         <v>183</v>
       </c>
@@ -2132,7 +2131,7 @@
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E29" t="s">
         <v>0</v>
@@ -2143,7 +2142,7 @@
       <c r="G29" s="1">
         <v>41570</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29">
         <f t="shared" si="1"/>
         <v>183</v>
       </c>
@@ -2195,7 +2194,7 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B41" t="s">
         <v>2</v>
@@ -2215,7 +2214,7 @@
       <c r="G41" s="1">
         <v>41563</v>
       </c>
-      <c r="H41" s="3">
+      <c r="H41">
         <f t="shared" ref="H41" si="2">G41-F41</f>
         <v>205</v>
       </c>
